--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-08-18 by build_data_coverage.py</t>
+          <t>Regenerated 2026-08-19 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -646,6 +646,20 @@
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>6. K-RERA embeds its entire 9,888-project index client-side, giving a promoter-to-projects map for the whole state in one request -- the opposite of Gujarat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>7. MCA charge filings were on the ZaubaCorp page all along. A real promoter shows 4 OPEN charges totalling ~Rs 90.3 crore to HDFC Bank and Catalyst Trusteeship -- free, no extra request, and the only independent check on a declared mortgage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>8. Group membership CANNOT be derived from a brand name. Searching 'PRANAMI' returns a Delhi hydro-power firm, a Gujarat non-profit and a Maharashtra castings company. Propose by name, confirm by shared director / registered office / filed relationship -- and treat a shared address as the weakest of the three (28 of 65 'group companies' were address-only).</t>
         </is>
       </c>
     </row>
@@ -2190,9 +2204,9 @@
           <t>ZaubaCorp (same page)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2200,19 +2214,19 @@
           <t>Free</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>observed</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>(unmapped -- Phase 4d)</t>
+          <t>company_profile_check.charges</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>NOT PARSED YET. Page is already fetched. Covers corporate promoters nationally.</t>
+          <t>NOW PARSED. Live on a real promoter: 4 OPEN charges, ~Rs 90.3 crore, to HDFC Bank and Catalyst Trusteeship. No closure date = live encumbrance. The only independent check on a promoter's declared mortgage -- the RERA record gives an area and never a lender.</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2401,12 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>MCA charge filings</t>
+          <t>Group entity graph (confirmed vs proposed)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>ZaubaCorp, national</t>
+          <t>group_entities.py</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -2402,7 +2416,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>fsi_metrics.mortgage_lender has no independent source today; a charge lookup names the lender.</t>
+          <t>BUILT. Propose by brand name, confirm by shared director / office / filed relationship. Link strength tiered -- address-only links excluded from sweeps.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D - Available but unused" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,12 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-08-19 by build_data_coverage.py</t>
+          <t>Regenerated 2026-08-21 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>unaudited        nobody has looked. 26 of ~30 state portals are here.</t>
+          <t>unaudited        nobody has looked. 24 of ~30 state portals are here.</t>
         </is>
       </c>
     </row>
@@ -660,6 +660,20 @@
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>8. Group membership CANNOT be derived from a brand name. Searching 'PRANAMI' returns a Delhi hydro-power firm, a Gujarat non-profit and a Maharashtra castings company. Propose by name, confirm by shared director / registered office / filed relationship -- and treat a shared address as the weakest of the three (28 of 65 'group companies' were address-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>9. Two more states are live: Jharkhand (JHARERA) and West Bengal (WBRERA), taking coverage to six authorities. JHARERA is the only authority anywhere in this pipeline that files a professional's PAN as a plain readable field rather than a scanned card, and it also publishes a declared past-projects table and a genuine litigation disclosure per project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>10. Karnataka's order/judgment coverage grew from one register to five (15,600+ rows across order search, authority orders, AO orders, interim orders and complaints-under-process), including a penalty table naming the violation, section and amount -- the single most consequential regulatory-history record any authority here publishes. JHARERA and WBRERA orders are now searchable by promoter too; WBRERA's join runs through its cause lists, since its own order register names no party directly.</t>
         </is>
       </c>
     </row>
@@ -674,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -682,8 +696,10 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -696,7 +712,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Yes / Partial / No / Not published / Unaudited. 'Unaudited' means nobody has looked yet -- 26 of ~30 state portals are in that state.</t>
+          <t>Yes / Partial / No / Not published / Unaudited. 'Unaudited' means nobody has looked yet -- 24 of ~30 state portals are in that state.</t>
         </is>
       </c>
     </row>
@@ -728,10 +744,20 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
+          <t>JHARERA</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>WBRERA</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>Charter facts field</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -763,12 +789,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -796,12 +832,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields.registration_number</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>TG-RERA's public record does not display its own registration number; search is by project name.</t>
         </is>
@@ -833,12 +879,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>corporate_identity</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>K-RERA publishes partner PANs and land-owner SHARES -- neither appears on a MahaRERA record.</t>
         </is>
@@ -870,14 +926,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>local_planning.professionals_of_record</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>GujRERA splits these across englist/calist/acrchlist/contr; the adapter normalises to one list.</t>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>GujRERA splits these across englist/calist/acrchlist/contr; the adapter normalises to one list. JHARERA is the only authority here that files a professional's PAN as a plain text field -- for the contractor, architect and structural engineer -- rather than a scanned card.</t>
         </is>
       </c>
     </row>
@@ -907,14 +973,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>land_identification</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA gives per-owner shares against survey numbers.</t>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA gives per-owner shares against survey numbers. WBRERA's project page carries no land/survey table; not captured by this adapter, and whether the portal itself publishes one at all is unaudited.</t>
         </is>
       </c>
     </row>
@@ -944,14 +1020,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Not built</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>rera_compliance.collection_account</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>TG-RERA publishes the 100% collection account but leaves the 70/30 split accounts blank.</t>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>TG-RERA publishes the 100% collection account but leaves the 70/30 split accounts blank. WBRERA's project page carries no bank-account table either -- same caveat as land details.</t>
         </is>
       </c>
     </row>
@@ -981,14 +1067,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>document_library</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>GujRERA 42/42 retrieved. K-RERA 112/152 -- the other 40 are LISTED but the portal serves 0 bytes.</t>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>GujRERA 42/42 retrieved. K-RERA 112/152 -- the other 40 are LISTED but the portal serves 0 bytes. JHARERA labels every document link 'View'; document_label() derives the real name from the surrounding table or header. WBRERA's links already carry real text, so no derivation is needed.</t>
         </is>
       </c>
     </row>
@@ -1018,14 +1114,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields.total_complaints_count</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA: use the STATE-WIDE /projectComplaintReport. The per-project page is NOT reliable -- it showed no complaints for a project the register lists with 12.</t>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA: use the STATE-WIDE /projectComplaintReport. The per-project page is NOT reliable -- it showed no complaints for a project the register lists with 12. JHARERA has no per-project count either; the adapter name-matches the promoter against the state-wide disposed-complaint register, which yields POSSIBLE matches to confirm, not a confirmed count. WBRERA publishes no complaint register through this interface at all -- recorded as None, never 0.</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1161,22 @@
           <t>Not published</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields.total_appeals_count</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1083,19 +1199,29 @@
           <t>Not published</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>sources[] (topic=litigation)</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA /viewAllJudgements exists; the adapter reads complaints but not judgements yet.</t>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA now reads FIVE promoter-keyed registers (order search, authority orders, AO orders, interim orders, complaints under process) -- 15,600+ rows including a penalty table naming the violation, section and amount. JHARERA's judgement/order register is searchable by promoter, though a share of rows name both parties in one unsplit column and are therefore invisible to that search. WBRERA's order register names no party at all; the join runs through its cause lists instead, so its coverage note matters more than its row count.</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1251,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>promoter_portfolio</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA embeds the WHOLE state index client-side (9,888 projects with promoter names), so a portfolio is one request. GujRERA confirmed absent.</t>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA embeds the WHOLE state index client-side (9,888 projects with promoter names), so a portfolio is one request. GujRERA confirmed absent. WBRERA publishes no promoter search and its state index does not name the promoter either, so a portfolio there would mean opening all ~4,700 project pages -- the adapter returns None and says why rather than sampling a partial set.</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1298,22 @@
           <t>Not published</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>promoter_portfolio.totals</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1190,19 +1336,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>(unmapped -- see Charter Mapping sheet)</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>GujRERA findoc block. MahaRERA publishes nothing equivalent. Highest-value differential finding.</t>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>GujRERA findoc block. MahaRERA publishes nothing equivalent. Highest-value differential finding. JHARERA also files an audited balance sheet as a downloadable document, labelled directly on the project page.</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1388,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>GujRERA findoc block.</t>
         </is>
@@ -1269,14 +1435,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>GujRERA findoc block.</t>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>GujRERA findoc block. JHARERA files three years of income-tax returns per project, also as downloadable documents.</t>
         </is>
       </c>
     </row>
@@ -1301,19 +1477,29 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA /viewDefaultProjects -- observed, not yet built. No other authority publishes one.</t>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA /viewDefaultProjects -- observed, not yet built. JHARERA's REJECTED and SURRENDERED registers are the closest equivalent: their URLs are imported into the adapter but nothing fetches them yet. WBRERA's defaulters list (17 rejected/defaulting applications by name) IS parsed by adapter_westbengal.fetch_defaulters(), but that function is called from nowhere in acquire() or the litigation sweep -- written, untested against a live page, and unused.</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1524,27 @@
           <t>No</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>K-RERA /unregProjectList -- observed, not yet built.</t>
         </is>
@@ -1370,7 +1566,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1380,12 +1576,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>K-RERA publishes both, per particular. Direct input to the financial-strength sub-metric.</t>
         </is>
@@ -1417,12 +1623,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>K-RERA detail page carries a delay-reason table.</t>
         </is>
@@ -1454,12 +1670,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>K-RERA tracks NOC validity dates and whether renewed.</t>
         </is>
@@ -1476,7 +1702,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1491,18 +1717,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>rera_compliance.construction_progress</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Not confirmed either way for JHARERA or WBRERA -- neither adapter currently extracts a QPR-equivalent field, and nobody has checked whether either portal even publishes one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G25"/>
+  <autoFilter ref="A4:I25"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1582,7 +1822,7 @@
           <t>Maha Bhulekh Property Card (हक्काचा मूळ धारक)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1614,7 +1854,7 @@
           <t>Maha Bhulekh Property Card (क्षेत्र चौ.मी.)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1646,7 +1886,7 @@
           <t>Maha Bhulekh Property Card (धारणाधिकार)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1678,7 +1918,7 @@
           <t>Maha Bhulekh Property Card (इतर भार)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1710,7 +1950,7 @@
           <t>Maha Bhulekh Property Card (फेरफार table)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1752,7 +1992,7 @@
           <t>Free + CAPTCHA</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -1784,7 +2024,7 @@
           <t>Free + CAPTCHA</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -1816,7 +2056,7 @@
           <t>Free -- page already fetched</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -1838,7 +2078,7 @@
           <t>Dharani (TG) / Bhoomi (KA) / AnyROR (GJ) / Bhulekh (UP)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
@@ -1848,7 +2088,7 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>unaudited</t>
         </is>
@@ -2278,7 +2518,7 @@
           <t>ICRA / Infomerics press releases</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2288,7 +2528,7 @@
           <t>Free</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -2320,7 +2560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2473,7 +2713,7 @@
           <t>Same -- a regulator-declared adverse signal.</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2500,7 +2740,7 @@
           <t>Free route to revenue/debt/net-worth figures the MCA charges for.</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2554,7 +2794,7 @@
           <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere.</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2587,8 +2827,89 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>JHARERA audited balance sheet + 3 years ITR</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Jharkhand projects</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>JHARERA rejected + surrendered registration lists</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Jharkhand projects</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>WBRERA defaulters list</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal projects</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E12"/>
+  <autoFilter ref="A4:E15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D - Available but unused" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$15</definedName>
@@ -73,17 +73,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-08-21 by build_data_coverage.py</t>
+          <t>Regenerated 2026-08-24 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>unaudited        nobody has looked. 24 of ~30 state portals are here.</t>
+          <t>unaudited        nobody has looked. ~20 of ~30 state portals are here, and so are individual rows on UP-RERA, TNRERA, HARERA and Delhi-RERA.</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,19 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>9. Two more states are live: Jharkhand (JHARERA) and West Bengal (WBRERA), taking coverage to six authorities. JHARERA is the only authority anywhere in this pipeline that files a professional's PAN as a plain readable field rather than a scanned card, and it also publishes a declared past-projects table and a genuine litigation disclosure per project.</t>
+          <t>9. Two more states are live: Jharkhand (JHARERA) and West Bengal (WBRERA), taking coverage to six authorities at the time. JHARERA is the only authority anywhere in this pipeline that files a professional's PAN as a plain readable field rather than a scanned card, and it also publishes a declared past-projects table and a genuine litigation disclosure per project.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>9b. FOUR more states are live as of 2026-08-24 -- Uttar Pradesh, Tamil Nadu, Haryana and Delhi -- taking coverage to TEN authorities. Each brings something no other one here does. HARERA states the promoter's CIN outright, which is the only hard RERA-to-MCA join in this pipeline; every other authority forces a name match. UP-RERA publishes the project bank account IN FULL and a khasra-level land grid. TNRERA publishes three separate order registers, all naming both parties. Delhi-RERA publishes almost nothing per project -- 130 projects for the whole NCT and no reachable detail record -- which is itself the finding: an absence from Delhi's register is close to worthless as evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>10. Karnataka's order/judgment coverage grew from one register to five (15,600+ rows across order search, authority orders, AO orders, interim orders and complaints-under-process), including a penalty table naming the violation, section and amount -- the single most consequential regulatory-history record any authority here publishes. JHARERA and WBRERA orders are now searchable by promoter too; WBRERA's join runs through its cause lists, since its own order register names no party directly.</t>
         </is>
@@ -688,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -698,8 +705,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="62" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="62" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -712,7 +723,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Yes / Partial / No / Not published / Unaudited. 'Unaudited' means nobody has looked yet -- 24 of ~30 state portals are in that state.</t>
+          <t>Yes / Partial / No / Not published / Unaudited. 'Unaudited' means nobody has looked yet -- ~20 of ~30 state portals are in that state, and so are whole data items on the four newest authorities.</t>
         </is>
       </c>
     </row>
@@ -754,10 +765,30 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
+          <t>UP-RERA</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>TNRERA</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>HARERA</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Delhi-RERA</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
           <t>Charter facts field</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -799,12 +830,36 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>Delhi-RERA is Partial because there is no per-project record at all: the register's own View control is inert and every detail route probed returns nothing, so a Delhi project's identity is its register row and nothing more.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -817,7 +872,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -842,14 +897,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields.registration_number</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>TG-RERA's public record does not display its own registration number; search is by project name.</t>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>TG-RERA's public record does not display its own registration number; search is by project name. UP-RERA is Partial: a legacy UPRERAPRJ number resolves with no search at all (the detail page id is the number's own numeric suffix), but the scheme used since ~2024 (UPRERAPRJ378870/03/2025) does not follow that and cannot be resolved here.</t>
         </is>
       </c>
     </row>
@@ -889,12 +964,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>corporate_identity</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>K-RERA publishes partner PANs and land-owner SHARES -- neither appears on a MahaRERA record.</t>
         </is>
@@ -911,7 +1006,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -936,12 +1031,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t>local_planning.professionals_of_record</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>GujRERA splits these across englist/calist/acrchlist/contr; the adapter normalises to one list. JHARERA is the only authority here that files a professional's PAN as a plain text field -- for the contractor, architect and structural engineer -- rather than a scanned card.</t>
         </is>
@@ -978,19 +1093,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>land_identification</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA gives per-owner shares against survey numbers. WBRERA's project page carries no land/survey table; not captured by this adapter, and whether the portal itself publishes one at all is unaudited.</t>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA gives per-owner shares against survey numbers. WBRERA's project page carries no land/survey table; not captured by this adapter, and whether the portal itself publishes one at all is unaudited. UP-RERA publishes a KHASRA/PLOT grid with per-parcel areas and a registry/agreement grid. HARERA carries DTCP licence numbers rather than khasra numbers. Note these are the promoter's own declaration in every case, not an independent land record.</t>
         </is>
       </c>
     </row>
@@ -1025,19 +1160,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>rera_compliance.collection_account</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>TG-RERA publishes the 100% collection account but leaves the 70/30 split accounts blank. WBRERA's project page carries no bank-account table either -- same caveat as land details.</t>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>TG-RERA publishes the 100% collection account but leaves the 70/30 split accounts blank. WBRERA's project page carries no bank-account table either -- same caveat as land details. UP-RERA publishes the project account number in full with bank and branch. TNRERA masks it (XXXXXXXXXX9995) while naming the bank, branch and the account holder.</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1207,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1077,14 +1232,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>document_library</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>GujRERA 42/42 retrieved. K-RERA 112/152 -- the other 40 are LISTED but the portal serves 0 bytes. JHARERA labels every document link 'View'; document_label() derives the real name from the surrounding table or header. WBRERA's links already carry real text, so no derivation is needed.</t>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>GujRERA 42/42 retrieved. K-RERA 112/152 -- the other 40 are LISTED but the portal serves 0 bytes. JHARERA labels every document link 'View'; document_label() derives the real name from the surrounding table or header. WBRERA's links already carry real text, so no derivation is needed. UP-RERA's grid has a third state besides filed and missing: 7 of 31 rows on a real record carry the promoter's own 'NA', including the CA, ARCHITECT and ENGINEERS certificates -- not filed, which is a finding rather than a gap. HARERA links 60 documents on one Gurugram record.</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1274,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
@@ -1114,24 +1289,44 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields.total_complaints_count</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA: use the STATE-WIDE /projectComplaintReport. The per-project page is NOT reliable -- it showed no complaints for a project the register lists with 12. JHARERA has no per-project count either; the adapter name-matches the promoter against the state-wide disposed-complaint register, which yields POSSIBLE matches to confirm, not a confirmed count. WBRERA publishes no complaint register through this interface at all -- recorded as None, never 0.</t>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA: use the STATE-WIDE /projectComplaintReport. The per-project page is NOT reliable -- it showed no complaints for a project the register lists with 12. JHARERA has no per-project count either; the adapter name-matches the promoter against the state-wide disposed-complaint register, which yields POSSIBLE matches to confirm, not a confirmed count. WBRERA publishes no complaint register through this interface at all -- recorded as None, never 0. TNRERA publishes THREE order registers (Authority, single-member bench, Adjudicating Officer) and Delhi-RERA one, all naming complainant AND respondent in their own columns -- which is what makes them promoter-searchable. UP-RERA and HARERA both gate their case search behind a CAPTCHA keyed on a case number, so complaints there are UNKNOWN rather than absent.</t>
         </is>
       </c>
     </row>
@@ -1146,37 +1341,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>rera_core_fields.total_appeals_count</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1189,12 +1404,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
@@ -1209,17 +1424,37 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>sources[] (topic=litigation)</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>K-RERA now reads FIVE promoter-keyed registers (order search, authority orders, AO orders, interim orders, complaints under process) -- 15,600+ rows including a penalty table naming the violation, section and amount. JHARERA's judgement/order register is searchable by promoter, though a share of rows name both parties in one unsplit column and are therefore invisible to that search. WBRERA's order register names no party at all; the join runs through its cause lists instead, so its coverage note matters more than its row count.</t>
         </is>
@@ -1236,12 +1471,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1256,19 +1491,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>promoter_portfolio</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>K-RERA embeds the WHOLE state index client-side (9,888 projects with promoter names), so a portfolio is one request. GujRERA confirmed absent. WBRERA publishes no promoter search and its state index does not name the promoter either, so a portfolio there would mean opening all ~4,700 project pages -- the adapter returns None and says why rather than sampling a partial set.</t>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>K-RERA embeds the WHOLE state index client-side (9,888 projects with promoter names), so a portfolio is one request. GujRERA confirmed absent. WBRERA publishes no promoter search and its state index does not name the promoter either, so a portfolio there would mean opening all ~4,700 project pages -- the adapter returns None and says why rather than sampling a partial set. UP-RERA's register is CAPTCHA-gated AND demands a district before a promoter, so a portfolio would need a solved CAPTCHA and one request per district across 75 districts. TNRERA is Partial: no promoter id and no promoter search, so a portfolio is a NAME match across year tables and every row is a candidate.</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1538,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1293,7 +1548,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Not published</t>
         </is>
@@ -1308,12 +1563,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>promoter_portfolio.totals</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1321,12 +1596,12 @@
           <t>AUDITED BALANCE SHEET</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1336,7 +1611,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1346,17 +1621,37 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t>(unmapped -- see Charter Mapping sheet)</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>GujRERA findoc block. MahaRERA publishes nothing equivalent. Highest-value differential finding. JHARERA also files an audited balance sheet as a downloadable document, labelled directly on the project page.</t>
         </is>
@@ -1368,12 +1663,12 @@
           <t>Audited profit &amp; loss statement</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1383,27 +1678,47 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>GujRERA findoc block.</t>
         </is>
@@ -1415,12 +1730,12 @@
           <t>Income-tax returns</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1430,7 +1745,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1440,17 +1755,37 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>GujRERA findoc block. JHARERA files three years of income-tax returns per project, also as downloadable documents.</t>
         </is>
@@ -1462,42 +1797,62 @@
           <t>Defaulters list</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>K-RERA /viewDefaultProjects -- observed, not yet built. JHARERA's REJECTED and SURRENDERED registers are the closest equivalent: their URLs are imported into the adapter but nothing fetches them yet. WBRERA's defaulters list (17 rejected/defaulting applications by name) IS parsed by adapter_westbengal.fetch_defaulters(), but that function is called from nowhere in acquire() or the litigation sweep -- written, untested against a live page, and unused.</t>
         </is>
@@ -1509,42 +1864,62 @@
           <t>Projects under investigation</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>K-RERA /unregProjectList -- observed, not yet built.</t>
         </is>
@@ -1556,17 +1931,17 @@
           <t>Cost incurred vs estimated cost</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1576,22 +1951,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>K-RERA publishes both, per particular. Direct input to the financial-strength sub-metric.</t>
         </is>
@@ -1603,17 +1998,17 @@
           <t>Delay reasons (promoter-declared)</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1623,22 +2018,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>K-RERA detail page carries a delay-reason table.</t>
         </is>
@@ -1650,17 +2065,17 @@
           <t>NOC expiry and renewal tracking</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1670,22 +2085,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
         <is>
           <t>(unmapped)</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>K-RERA tracks NOC validity dates and whether renewed.</t>
         </is>
@@ -1702,7 +2137,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1717,32 +2152,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>Unaudited</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Unaudited</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>Unaudited</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>rera_compliance.construction_progress</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>Not confirmed either way for JHARERA or WBRERA -- neither adapter currently extracts a QPR-equivalent field, and nobody has checked whether either portal even publishes one.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I25"/>
+  <autoFilter ref="A4:M25"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1822,7 +2277,7 @@
           <t>Maha Bhulekh Property Card (हक्काचा मूळ धारक)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1854,7 +2309,7 @@
           <t>Maha Bhulekh Property Card (क्षेत्र चौ.मी.)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1886,7 +2341,7 @@
           <t>Maha Bhulekh Property Card (धारणाधिकार)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1918,7 +2373,7 @@
           <t>Maha Bhulekh Property Card (इतर भार)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1950,7 +2405,7 @@
           <t>Maha Bhulekh Property Card (फेरफार table)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1992,7 +2447,7 @@
           <t>Free + CAPTCHA</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -2024,7 +2479,7 @@
           <t>Free + CAPTCHA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -2056,7 +2511,7 @@
           <t>Free -- page already fetched</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -2078,7 +2533,7 @@
           <t>Dharani (TG) / Bhoomi (KA) / AnyROR (GJ) / Bhulekh (UP)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
@@ -2088,7 +2543,7 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>unaudited</t>
         </is>
@@ -2481,7 +2936,7 @@
           <t>MCA (paid) / Tofler / InstaFinancials (paywalled)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2518,7 +2973,7 @@
           <t>ICRA / Infomerics press releases</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -2528,7 +2983,7 @@
           <t>Free</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>observed</t>
         </is>
@@ -2713,7 +3168,7 @@
           <t>Same -- a regulator-declared adverse signal.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2740,7 +3195,7 @@
           <t>Free route to revenue/debt/net-worth figures the MCA charges for.</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2794,7 +3249,7 @@
           <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere.</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2875,7 +3330,7 @@
           <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2902,7 +3357,7 @@
           <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-08-24 by build_data_coverage.py</t>
+          <t>Regenerated 2026-08-27 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -681,6 +681,13 @@
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>10. Karnataka's order/judgment coverage grew from one register to five (15,600+ rows across order search, authority orders, AO orders, interim orders and complaints-under-process), including a penalty table naming the violation, section and amount -- the single most consequential regulatory-history record any authority here publishes. JHARERA and WBRERA orders are now searchable by promoter too; WBRERA's join runs through its cause lists, since its own order register names no party directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>11. The 32 'Unaudited' cells UP-RERA/TNRERA/HARERA/Delhi-RERA picked up on 2026-08-24 were actually audited live on 2026-08-26, one portal at a time, rather than left to sit. Each of the four states turned out to have a real Appellate Tribunal separate from the RERA authority itself -- HARERA's (HREAT) is plainly browsable and promoter-searchable, UP's (UP-REAT) is CAPTCHA-gated, Delhi's (REAT) is browsable but names no party, and Tamil Nadu's exists but publishes nothing searchable at all. Every one of the four also turned out to publish SOME form of defaulter/enforcement register the earlier audit had not found -- UP-RERA's DefaulterList (72 rows, reachable only via an ASP.NET postback, not a link), HARERA's cancelled/defaulter register (confirmed DISTINCT from its already-known lapsed-projects register, which is validity expiry rather than an authority action), TNRERA's penalty register (147 rows), and Delhi's execution register (7,493 rows) plus its suo-moto register (1,797 rows, the clearest 'projects under investigation' signal of the four). None of these seven new registers is wired into acquire() yet -- each earned an unwired, live-verified parser function instead, the same precedent WBRERA's fetch_defaulters() set, and each is its own row on Sheet D. What stayed genuinely negative also got a real reason instead of a shrug: none of the four publishes a P&amp;L statement or an income-tax return anywhere, UP-RERA and Delhi-RERA publish no balance sheet either, and none but K-RERA states an NOC EXPIRY date (HARERA's 'Statutory Approvals' table gives the date obtained, not the date it lapses).</t>
         </is>
       </c>
     </row>
@@ -1366,24 +1373,24 @@
           <t>Not published</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -1391,7 +1398,11 @@
           <t>rera_core_fields.total_appeals_count</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr"/>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>TNRERA is No, audited live 2026-08-26: a Tamil Nadu Real Estate Appellate Tribunal (TNREAT) DOES exist, distinct from the authority -- it has its own domain, tnreat.tn.gov.in, linked from TNRERA's own homepage -- but its public page carries no case search, cause list or judgment register at all, only a sign-in and a virtual-meeting-report link. Not a stub of the authority's own order registers: a genuinely separate body that simply publishes nothing searchable to the public. UP-RERA is Partial: its own Appellate Tribunal (UP-REAT) runs a live judgement search at efilingreat.up.gov.in/upreat/judgement.php with a free-text party-name field, CAPTCHA-gated. CONFIRMED LIVE 2026-08-26 the gate is passable, not just present: up_captcha_search.py opens a real browser, a human reads and solves the CAPTCHA, and the search genuinely runs -- tested against BALAJIMAHIMA INFRATECH PRIVATE LIMITED, which returned a clean 'No Data Found' in a real results table (Sr.No/Filing No./Case No./Case Title/Registration Date/Action), not an error or an empty page. Stays Partial rather than Yes because every search still costs one human CAPTCHA solve -- real and working, but not unattended. HARERA is Yes: the Haryana Real Estate Appellate Tribunal is served off HARERA's own domain (haryanarera.gov.in/admincontrol/judgements/3), a plain GET with no CAPTCHA -- 2,779 rows of Appeal No. / Appellant Name / Respondent Name / Date of Decision, confirmed promoter-searchable. Delhi-RERA is now Yes, upgraded from Partial 2026-08-26: REAT Delhi (shared with the UT of Chandigarh, not linked from any Delhi-RERA page, found only by web search) publishes a live 505-row register that names no party in its own columns -- but every row links a scanned judgement PDF, and REAT's own case captions name the Appellant and Respondent on the PDF's first page. states/adapter_delhi.py's build_appeal_party_index() downloads and OCRs (PyMuPDF native text first, Tesseract fallback -- confirmed live that every PDF sampled is a scan, zero native text) just that first page across all 481 distinct order PDFs behind the 505 rows, extracting both party names by the caption's own structure rather than guessing at fixed columns. Confirmed live 2026-08-26: 437/505 rows (87%) now carry a real party name -- searching 'Parsvnath' returns 27 real hits, e.g. 'Bimal Kumar &amp; Ors. vs M/s Parsvnath Landmark Developers Pvt. Ltd.' Of the 68 rows that don't, 63 are the AUTHORITY'S OWN register linking a PDF that 404s (a genuine broken link on their side, confirmed directly), and only 5 PDFs (12 rows, all 2021-2022 vintage) use a caption shape the parser doesn't recognise. search_appeals_by_party() is the promoter-facing search this unlocks, still unwired into acquire().</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1496,9 +1507,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -1523,7 +1534,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>K-RERA embeds the WHOLE state index client-side (9,888 projects with promoter names), so a portfolio is one request. GujRERA confirmed absent. WBRERA publishes no promoter search and its state index does not name the promoter either, so a portfolio there would mean opening all ~4,700 project pages -- the adapter returns None and says why rather than sampling a partial set. UP-RERA's register is CAPTCHA-gated AND demands a district before a promoter, so a portfolio would need a solved CAPTCHA and one request per district across 75 districts. TNRERA is Partial: no promoter id and no promoter search, so a portfolio is a NAME match across year tables and every row is a candidate.</t>
+          <t>K-RERA embeds the WHOLE state index client-side (9,888 projects with promoter names), so a portfolio is one request. GujRERA confirmed absent. WBRERA publishes no promoter search and its state index does not name the promoter either, so a portfolio there would mean opening all ~4,700 project pages -- the adapter returns None and says why rather than sampling a partial set. UP-RERA is now Partial rather than No: CONFIRMED LIVE 2026-08-26 via a human-solved CAPTCHA (up_captcha_search.py) that the search genuinely works, correctly returning UPRERAPRJ14636 (BALAJI GREENS) for BALAJIMAHIMA INFRATECH PRIVATE LIMITED in Barabanki district. It stays Partial, not Yes, because it demands a district before a promoter, so a full portfolio would need a solved CAPTCHA per district across 75 districts -- unattended automation is still refused (group_sweep._CANNOT_SEARCH), but a human-in-the-loop lookup is a real, working path now, not merely a theoretical one. TNRERA is Partial for a different reason: no promoter id and no promoter search, so a portfolio is a NAME match across year tables and every row is a candidate.</t>
         </is>
       </c>
     </row>
@@ -1626,14 +1637,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -1653,7 +1664,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>GujRERA findoc block. MahaRERA publishes nothing equivalent. Highest-value differential finding. JHARERA also files an audited balance sheet as a downloadable document, labelled directly on the project page.</t>
+          <t>GujRERA findoc block. MahaRERA publishes nothing equivalent. Highest-value differential finding. JHARERA also files an audited balance sheet as a downloadable document, labelled directly on the project page. TNRERA is No, audited live 2026-08-26 against TNRERA/29/BLG/0001/2026, /0004/2026 and /0005/2026: the promoter view carries a 'Financial Indicators (Rs. in Lakhs)' block with a bare self-declared Net Worth NUMBER (populated on one of three: Rs 2,00,00,000) but no uploaded balance-sheet document anywhere in the documents list on any of the three projects checked. UP-RERA is No: the document grid was read on three real projects (51 rows, 20 distinct labels) and none resembles a balance sheet -- the closest is the Form REG-3 CA certificate, which certifies compliance rather than filing the statement itself. HARERA's Yes is real but softer than GujRERA's or JHARERA's actual uploaded statements: it rests on a Part-D compliance declaration ('Annex copy of the balance sheet of last 3 years: Yes') and a CA-certificate document referencing 'BOOKS OF ACCOUNTS/ BALANCE SHEET' -- no document in the 60-row library checked is itself labelled 'balance sheet'.</t>
         </is>
       </c>
     </row>
@@ -1693,19 +1704,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
@@ -1720,7 +1731,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>GujRERA findoc block.</t>
+          <t>GujRERA findoc block. TNRERA is No, same 'Financial Indicators' block and same three projects: 'Net Profit / Loss' is a bare self-declared number (Rs 72,16,670 on the one populated record), never a filed P&amp;L statement. UP-RERA is No, same three-project document-grid read as above. HARERA is No: 'profit and loss'/'profit &amp; loss' occurs zero times across four project detail pages checked (1444, 681, 3723, 431), against a single 'balance sheet' mention each -- the two are not filed together.</t>
         </is>
       </c>
     </row>
@@ -1760,19 +1771,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
@@ -1787,7 +1798,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>GujRERA findoc block. JHARERA files three years of income-tax returns per project, also as downloadable documents.</t>
+          <t>GujRERA findoc block. JHARERA files three years of income-tax returns per project, also as downloadable documents. TNRERA is No, same block: 'Taxes Paid - IT (GST/ST)' is a single number that conflates income tax with GST/service tax (Rs 27,92,915 on the populated record) and no ITR document is filed anywhere in the three document sets checked. UP-RERA is No, same document-grid read. HARERA is No: 'income tax'/'ITR' occurs zero times across the same four pages.</t>
         </is>
       </c>
     </row>
@@ -1827,24 +1838,24 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
@@ -1854,7 +1865,7 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>K-RERA /viewDefaultProjects -- observed, not yet built. JHARERA's REJECTED and SURRENDERED registers are the closest equivalent: their URLs are imported into the adapter but nothing fetches them yet. WBRERA's defaulters list (17 rejected/defaulting applications by name) IS parsed by adapter_westbengal.fetch_defaulters(), but that function is called from nowhere in acquire() or the litigation sweep -- written, untested against a live page, and unused.</t>
+          <t>K-RERA /viewDefaultProjects -- observed, not yet built. JHARERA's REJECTED and SURRENDERED registers are the closest equivalent: their URLs are imported into the adapter but nothing fetches them yet. WBRERA's defaulters list (17 rejected/defaulting applications by name) IS parsed by adapter_westbengal.fetch_defaulters(), but that function is called from nowhere in acquire() or the litigation sweep -- written, untested against a live page, and unused. TNRERA is Yes, audited live 2026-08-26: https://rera.tn.gov.in/building/online/penalty and .../layout/online/penalty are live, unpaginated pages naming the promoter, address, project and penalty levied -- 1 row on Building (TNRERA/PBF/0092/2025, M/S. VIKAS MANTRA PROPERTIES &amp; INFRASTRUCTURE PRIVATE LIMITED, Rs 20,10,940, 13-02-2025) and 146 on Layout. Titled 'Penalty', not 'Defaulters' or 'Black List' -- no register under either of those names was found, and no separate revoked/cancelled-registration list exists. An unwired parser (parse_penalty_register / fetch_penalty_notices) was added to states/adapter_tamilnadu.py, mirroring adapter_westbengal.fetch_defaulters(). UP-RERA is Yes: https://www.up-rera.in/DefaulterList (reachable only via the homepage's DE-REGISTERED PROJECTS postback, not a plain link) serves a live 72-row register -- reg. no., project name suffixed '(De-Registered Project)' or '(Defaulter Project)', district, promoter -- e.g. UPRERAPRJ7090, ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED. An unwired fetch_defaulters() was added to states/adapter_uttarpradesh.py. HARERA is Yes: /admincontrol/cancelled_projects/{bench} (menu label 'Defaulter/ Cancelled/ Suspended/ Abeyance Projects') is a distinct, live register -- 23 Panchkula + 5 Gurugram rows -- confirmed DIFFERENT from /admincontrol/lapsed_projects/{bench} (319 + 234 rows), which is only registrations whose validity date has passed, not a defaulter finding; both got unwired parsers in states/adapter_haryana.py. Delhi-RERA is Partial: the authority never uses the word 'defaulter', but courtview/ExecutionInOrderJudgementsAuthorityInfo -- 7,493 live rows of orders referred for enforcement because the promoter ('Judgement Debtor') did not comply -- is the closest real equivalent; got an unwired parser in states/adapter_delhi.py.</t>
         </is>
       </c>
     </row>
@@ -1894,24 +1905,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -1921,7 +1932,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>K-RERA /unregProjectList -- observed, not yet built.</t>
+          <t>K-RERA /unregProjectList -- observed, not yet built. TNRERA stays Partial, but 'static (non-searchable)' is fixed as of 2026-08-26: both PDFs are NATIVE TEXT (confirmed live, zero OCR needed, unlike Delhi-RERA's REAT scans) and adapter_tamilnadu.py's parse_enforcement_pdf()/search_enforcement_lists_by_name() reads them with pdfplumber's table extraction -- 35 rows off the 5-page SCN list, 1,502 off the 118-page caution list, confirmed live end-to-end (searching 'Sivakaminathan' returns the real row). What did NOT change, because it is a finding about the authority's publication rather than a scraping gap: neither list covers a REGISTERED project under suo-moto scrutiny, only the unregistered-building enforcement pipeline -- 'Show Cause Notice issued for levy of penalty for non registration' and a 'Public Caution Notice' of buildings claimed as personal-use and therefore left unregistered. UP-RERA stays Partial for the opposite reason: the three adjacent registers (Abeyance, NCLT, Withdrawn Registration) named in the earlier audit are REAL pages, but their data loads via a WebService1.asmx POST that returned HTTP 500 on every parameter tried, including a real browser driving the page's own default (empty-parameter) call -- confirmed live 2026-08-26 this is the AUTHORITY'S OWN backend failing, not a request-shaping problem on this end, so nothing was built against a data source that cannot currently be read at all. HARERA is No: the only relevant menu item, 'Suo Motu (Projects) Cause List', is a hearing-schedule generator requiring a specific date and a CAPTCHA, not a browsable register; the only visible trace of suo-moto outcomes is inside HREAT's judgement text (case numbers containing 'MT' for Motu). Delhi-RERA is Yes: courtview/SuoMotoCases is a live, promoter-named, 1,797-row register of the authority's own-motion notices and orders -- the clearest 'projects under investigation' register found on any of the four new states; got an unwired parser in states/adapter_delhi.py.</t>
         </is>
       </c>
     </row>
@@ -2028,19 +2039,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
@@ -2055,7 +2066,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>K-RERA detail page carries a delay-reason table.</t>
+          <t>K-RERA detail page carries a delay-reason table. TNRERA is No, audited live against TN/29/Building/0328/2024 whose register row reads 'Extension given upto 31.07.2026 Completed': its detail view (public-view2) has no delay-reason, extension-reason or revised-completion-date field across any of its 20 sections -- the extension text lives only as free text in the register's own Current Status column, never as a structured field, and never states WHY. UP-RERA is No: 'delay'/'reason'/'extension'/'revised' were grepped across three project pages with zero hits for 'delay' or 'reason'; the only adjacent field is a bare revised valid-upto date with no promoter-declared justification. HARERA is Partial: the project detail page carries structured 'Initial date of completion' and 'Likely date of completion' fields -- a computable delay signal -- but 'reason'/'justification' occurs zero times anywhere on the page, so there is no promoter-declared free-text reason, only the two dates.</t>
         </is>
       </c>
     </row>
@@ -2095,19 +2106,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
@@ -2122,7 +2133,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>K-RERA tracks NOC validity dates and whether renewed.</t>
+          <t>K-RERA tracks NOC validity dates and whether renewed. TNRERA is revised from Partial to No, audited live 2026-08-26: the detail view does carry a 'Clearance / NOC Details' section, but its only fields are 'Clearance Type' (e.g. 'PWD &amp; RS') and 'Uploaded Document' -- confirmed on both a fresh 2026 registration and an already-extended 2024 one -- with no expiry date or renewal-status field anywhere in either. UP-RERA is No: zero genuine 'NOC' occurrences across three project pages and up-rera.in's full 153-link menu (the only raw-HTML hits were inside the base64 __VIEWSTATE blob). HARERA is No: the 'Statutory Approvals Status' table lists licence/clearance/NOC numbers each marked 'ALREADY BEEN OBTAINED' with a date -- but that date is when it was obtained, not an expiry or validity-end date, and no separate NOC-validity register exists.</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3363,8 +3374,197 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>UP-RERA de-registered/defaulter list</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh projects</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>HARERA cancelled/defaulter projects</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Haryana projects</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TNRERA penalty register</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu projects</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>TNRERA unregistered-project enforcement PDFs</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu projects/promoters</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Delhi-RERA suo-moto register</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Delhi projects</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Delhi-RERA execution register</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Delhi projects</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Delhi projects</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised.</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E15"/>
+  <autoFilter ref="A4:E22"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Regenerated 2026-08-27 by build_data_coverage.py</t>
+          <t>Regenerated 2026-08-31 by build_data_coverage.py</t>
         </is>
       </c>
     </row>
@@ -688,6 +688,27 @@
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>11. The 32 'Unaudited' cells UP-RERA/TNRERA/HARERA/Delhi-RERA picked up on 2026-08-24 were actually audited live on 2026-08-26, one portal at a time, rather than left to sit. Each of the four states turned out to have a real Appellate Tribunal separate from the RERA authority itself -- HARERA's (HREAT) is plainly browsable and promoter-searchable, UP's (UP-REAT) is CAPTCHA-gated, Delhi's (REAT) is browsable but names no party, and Tamil Nadu's exists but publishes nothing searchable at all. Every one of the four also turned out to publish SOME form of defaulter/enforcement register the earlier audit had not found -- UP-RERA's DefaulterList (72 rows, reachable only via an ASP.NET postback, not a link), HARERA's cancelled/defaulter register (confirmed DISTINCT from its already-known lapsed-projects register, which is validity expiry rather than an authority action), TNRERA's penalty register (147 rows), and Delhi's execution register (7,493 rows) plus its suo-moto register (1,797 rows, the clearest 'projects under investigation' signal of the four). None of these seven new registers is wired into acquire() yet -- each earned an unwired, live-verified parser function instead, the same precedent WBRERA's fetch_defaulters() set, and each is its own row on Sheet D. What stayed genuinely negative also got a real reason instead of a shrug: none of the four publishes a P&amp;L statement or an income-tax return anywhere, UP-RERA and Delhi-RERA publish no balance sheet either, and none but K-RERA states an NOC EXPIRY date (HARERA's 'Statutory Approvals' table gives the date obtained, not the date it lapses).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>12. WBRERA's two 'Not built' rows are now built and confirmed live 2026-08-31. Land Area and a full location block (address/district/block/police station/pincode) turned out to be structured fields on every project page sampled -- adapter_westbengal.land_details() now reads them. A dag/mouza/J.L. survey reference is genuinely inconsistent, embedded as free text in the project address on roughly a third of a six-district sample and absent from the rest, hence 'Partial' rather than 'Yes'. The bank-account row went the other way: checked across the same six-project sample and confirmed the authority publishes no escrow/collection account field at all, so it moves from 'Not built' to 'Not published' -- a finding about WBRERA, not a gap in this adapter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>13. WBRERA's document library was already downloading a real audited balance sheet and up to three years of ITRs for every one of 12 projects sampled live 2026-08-31 -- the gap was that company_charter.py's own high-priority-document keyword list never recognised WBRERA's bare 'ITR' filenames ('ITR_3 Years.pdf', 'itr with blance sheet ay 23-4 &amp; 24-25.pdf') as financial disclosure, so they were fetched but never text-extracted for the Charter pass. Fixed with an alpha-boundary regex rather than a plain substring (which would also fire on 'arbitration'/'distribution'/'contribution') or a strict word boundary (which would miss the live 'ITR_3'/'ITR_23-24' filenames, since '_' counts as a word character). AUDITED BALANCE SHEET and Income-tax returns both move from No to Yes for WB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>14. Five of the sheet's 'Unaudited' cells were closed out live 2026-08-31. Professionals of record and Past-experience declarations are both genuinely Not published on HARERA -- its REP-I form has no section asking for either, confirmed by listing every numbered heading on the form across 7 real projects, not just the absence of a keyword. Past-experience is ALSO Not published on UP-RERA and TNRERA, checked on 4 and 3 real projects respectively -- a different finding from 'Promoter's other projects (track record)' above, which is about finding a promoter's OTHER filings by name match rather than a self-declared history on this one. Construction progress/QPR moved three ways at once: JHARERA to Yes (a genuine per-unit 'Completion Status' column already flowing through the adapter's own 'units' table but never surfaced), WBRERA to Not published (the page only carries a site-wide notice that QPR filing is mandatory, never a per-project figure), and HARERA to Partial (a real but project-type-dependent percentage-completion/status field). The JHARERA portal itself went down mid-audit -- 3 of 4 fetch attempts against the same URL timed out -- a reminder that an unreachable portal during a check is not the same finding as a confirmed absence.</t>
         </is>
       </c>
     </row>
@@ -730,7 +751,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Yes / Partial / No / Not published / Unaudited. 'Unaudited' means nobody has looked yet -- ~20 of ~30 state portals are in that state, and so are whole data items on the four newest authorities.</t>
+          <t>Yes / Partial / Not published / Unaudited. 'Not published' replaced the earlier separate 'No' label 2026-08-31 -- both meant the same thing here (this authority does not publish this data item) and were used inconsistently row to row. 'Unaudited' means nobody has looked yet -- ~20 of ~30 state portals are in that state, and so are whole data items on the four newest authorities.</t>
         </is>
       </c>
     </row>
@@ -881,7 +902,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1015,7 +1036,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -1048,9 +1069,9 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
@@ -1065,7 +1086,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>GujRERA splits these across englist/calist/acrchlist/contr; the adapter normalises to one list. JHARERA is the only authority here that files a professional's PAN as a plain text field -- for the contractor, architect and structural engineer -- rather than a scanned card.</t>
+          <t>GujRERA splits these across englist/calist/acrchlist/contr; the adapter normalises to one list. JHARERA is the only authority here that files a professional's PAN as a plain text field -- for the contractor, architect and structural engineer -- rather than a scanned card. HARERA is Not published, audited live 2026-08-31 across 7 real Gurugram-bench projects (detail ids 1444, 1011, 2953, 1641, 1353, 1856, 2967) plus a full listing of every numbered section heading on the REP-I form: zero occurrences of 'architect' as a named professional on 6 of 7, and the one project where 'architect' does appear is only the phrase 'AS PER ARCHITECT CERTIFICATE ATTACHED' inside a construction-status remark, naming no one. 'Chartered Accountant' appears on every project, but only as the signer of a non-default certificate and a balance-sheet compliance certificate -- a role, not a named professional-of-record entry with a licence number the way MahaRERA's professionals table carries one. HARERA's REP-I form simply asks for none of this: company/director details, land/FAR, approvals, construction and sales status, financials and bank accounts, statutory approvals -- no architect/engineer/CA identity section anywhere in the form's own structure.</t>
         </is>
       </c>
     </row>
@@ -1100,9 +1121,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Not built</t>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -1132,7 +1153,7 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>K-RERA gives per-owner shares against survey numbers. WBRERA's project page carries no land/survey table; not captured by this adapter, and whether the portal itself publishes one at all is unaudited. UP-RERA publishes a KHASRA/PLOT grid with per-parcel areas and a registry/agreement grid. HARERA carries DTCP licence numbers rather than khasra numbers. Note these are the promoter's own declaration in every case, not an independent land record.</t>
+          <t>K-RERA gives per-owner shares against survey numbers. WBRERA is now Partial, built and confirmed live 2026-08-31: Land Area and a location block (address/district/block/police station/pincode) are structured and present on every project sampled, via adapter_westbengal.land_details(). A dag/mouza/J.L. survey reference is NOT structured -- it is free text sometimes embedded in the project address, present on roughly a third of a random six-district sample and absent from the rest, so land_reference_present says which case a given project is rather than reading empty. UP-RERA publishes a KHASRA/PLOT grid with per-parcel areas and a registry/agreement grid. HARERA carries DTCP licence numbers rather than khasra numbers. Note these are the promoter's own declaration in every case, not an independent land record.</t>
         </is>
       </c>
     </row>
@@ -1167,9 +1188,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Not built</t>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1199,7 +1220,7 @@
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>TG-RERA publishes the 100% collection account but leaves the 70/30 split accounts blank. WBRERA's project page carries no bank-account table either -- same caveat as land details. UP-RERA publishes the project account number in full with bank and branch. TNRERA masks it (XXXXXXXXXX9995) while naming the bank, branch and the account holder.</t>
+          <t>TG-RERA publishes the 100% collection account but leaves the 70/30 split accounts blank. WBRERA is revised from Not built to Not published, confirmed live 2026-08-31 across a random sample of six projects spanning six districts and registration years: 'account', 'escrow' and 'IFSC' occur zero times on any of them (the only 'bank' hits are the district-menu entry for Bankura). This is the authority never publishing the field at all, not an adapter gap -- adapter_westbengal.py now states this outright in _AUTHORITY_NOTES rather than leaving it to look like unfinished work. UP-RERA publishes the project account number in full with bank and branch. TNRERA masks it (XXXXXXXXXX9995) while naming the bank, branch and the account holder.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1237,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -1283,7 +1304,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1308,7 +1329,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -1318,7 +1339,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1350,7 +1371,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1380,7 +1401,7 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
@@ -1400,7 +1421,7 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>TNRERA is No, audited live 2026-08-26: a Tamil Nadu Real Estate Appellate Tribunal (TNREAT) DOES exist, distinct from the authority -- it has its own domain, tnreat.tn.gov.in, linked from TNRERA's own homepage -- but its public page carries no case search, cause list or judgment register at all, only a sign-in and a virtual-meeting-report link. Not a stub of the authority's own order registers: a genuinely separate body that simply publishes nothing searchable to the public. UP-RERA is Partial: its own Appellate Tribunal (UP-REAT) runs a live judgement search at efilingreat.up.gov.in/upreat/judgement.php with a free-text party-name field, CAPTCHA-gated. CONFIRMED LIVE 2026-08-26 the gate is passable, not just present: up_captcha_search.py opens a real browser, a human reads and solves the CAPTCHA, and the search genuinely runs -- tested against BALAJIMAHIMA INFRATECH PRIVATE LIMITED, which returned a clean 'No Data Found' in a real results table (Sr.No/Filing No./Case No./Case Title/Registration Date/Action), not an error or an empty page. Stays Partial rather than Yes because every search still costs one human CAPTCHA solve -- real and working, but not unattended. HARERA is Yes: the Haryana Real Estate Appellate Tribunal is served off HARERA's own domain (haryanarera.gov.in/admincontrol/judgements/3), a plain GET with no CAPTCHA -- 2,779 rows of Appeal No. / Appellant Name / Respondent Name / Date of Decision, confirmed promoter-searchable. Delhi-RERA is now Yes, upgraded from Partial 2026-08-26: REAT Delhi (shared with the UT of Chandigarh, not linked from any Delhi-RERA page, found only by web search) publishes a live 505-row register that names no party in its own columns -- but every row links a scanned judgement PDF, and REAT's own case captions name the Appellant and Respondent on the PDF's first page. states/adapter_delhi.py's build_appeal_party_index() downloads and OCRs (PyMuPDF native text first, Tesseract fallback -- confirmed live that every PDF sampled is a scan, zero native text) just that first page across all 481 distinct order PDFs behind the 505 rows, extracting both party names by the caption's own structure rather than guessing at fixed columns. Confirmed live 2026-08-26: 437/505 rows (87%) now carry a real party name -- searching 'Parsvnath' returns 27 real hits, e.g. 'Bimal Kumar &amp; Ors. vs M/s Parsvnath Landmark Developers Pvt. Ltd.' Of the 68 rows that don't, 63 are the AUTHORITY'S OWN register linking a PDF that 404s (a genuine broken link on their side, confirmed directly), and only 5 PDFs (12 rows, all 2021-2022 vintage) use a caption shape the parser doesn't recognise. search_appeals_by_party() is the promoter-facing search this unlocks, still unwired into acquire().</t>
+          <t>TNRERA is Not published, audited live 2026-08-26: a Tamil Nadu Real Estate Appellate Tribunal (TNREAT) DOES exist, distinct from the authority -- it has its own domain, tnreat.tn.gov.in, linked from TNRERA's own homepage -- but its public page carries no case search, cause list or judgment register at all, only a sign-in and a virtual-meeting-report link. Not a stub of the authority's own order registers: a genuinely separate body that simply publishes nothing searchable to the public. UP-RERA is Partial: its own Appellate Tribunal (UP-REAT) runs a live judgement search at efilingreat.up.gov.in/upreat/judgement.php with a free-text party-name field, CAPTCHA-gated. CONFIRMED LIVE 2026-08-26 the gate is passable, not just present: up_captcha_search.py opens a real browser, a human reads and solves the CAPTCHA, and the search genuinely runs -- tested against BALAJIMAHIMA INFRATECH PRIVATE LIMITED, which returned a clean 'No Data Found' in a real results table (Sr.No/Filing No./Case No./Case Title/Registration Date/Action), not an error or an empty page. Stays Partial rather than Yes because every search still costs one human CAPTCHA solve -- real and working, but not unattended. HARERA is Yes: the Haryana Real Estate Appellate Tribunal is served off HARERA's own domain (haryanarera.gov.in/admincontrol/judgements/3), a plain GET with no CAPTCHA -- 2,779 rows of Appeal No. / Appellant Name / Respondent Name / Date of Decision, confirmed promoter-searchable. Delhi-RERA is now Yes, upgraded from Partial 2026-08-26: REAT Delhi (shared with the UT of Chandigarh, not linked from any Delhi-RERA page, found only by web search) publishes a live 505-row register that names no party in its own columns -- but every row links a scanned judgement PDF, and REAT's own case captions name the Appellant and Respondent on the PDF's first page. states/adapter_delhi.py's build_appeal_party_index() downloads and OCRs (PyMuPDF native text first, Tesseract fallback -- confirmed live that every PDF sampled is a scan, zero native text) just that first page across all 481 distinct order PDFs behind the 505 rows, extracting both party names by the caption's own structure rather than guessing at fixed columns. Confirmed live 2026-08-26: 437/505 rows (87%) now carry a real party name -- searching 'Parsvnath' returns 27 real hits, e.g. 'Bimal Kumar &amp; Ors. vs M/s Parsvnath Landmark Developers Pvt. Ltd.' Of the 68 rows that don't, 63 are the AUTHORITY'S OWN register linking a PDF that 404s (a genuine broken link on their side, confirmed directly), and only 5 PDFs (12 rows, all 2021-2022 vintage) use a caption shape the parser doesn't recognise. search_appeals_by_party() is the promoter-facing search this unlocks, still unwired into acquire().</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1438,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1442,7 +1463,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -1452,7 +1473,7 @@
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1484,12 +1505,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1504,7 +1525,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -1551,7 +1572,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -1574,19 +1595,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
@@ -1599,7 +1620,11 @@
           <t>promoter_portfolio.totals</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>All three move from Unaudited to Not published, audited live 2026-08-31. UP-RERA: zero hits for 'experience'/'past project'/'completed project'/'track record' across four real detail pages (14636, 11528, 2499, plus two invalid ids returning the portal's own empty shell) -- matches the authority's own detail-page contents already documented in states/uttarpradesh.py (promoter identity, khasra grid, bank account, architect/engineer, documents, QPR certificates), which never mentions past experience either. TNRERA: zero hits across three real registrations spanning both the dynamic public-view2 project page and public-view1 promoter page (TN/29/Building/0328/2024) and a legacy static register entry (TN/16/Building/0001/2024) -- neither view's own section list (Financial Indicators, Promoter Detail, Approval Details, Project Bank Details, etc.) includes anything resembling past experience; this is a DIFFERENT data item from 'Promoter's other projects (track record)' above, which is about finding a promoter's OTHER TNRERA filings by name match, not a self-declared history filed with this application. HARERA: same REP-I heading sweep as Professionals of record above -- no section asks for it.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1609,12 +1634,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1632,19 +1657,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -1664,7 +1689,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>GujRERA findoc block. MahaRERA publishes nothing equivalent. Highest-value differential finding. JHARERA also files an audited balance sheet as a downloadable document, labelled directly on the project page. TNRERA is No, audited live 2026-08-26 against TNRERA/29/BLG/0001/2026, /0004/2026 and /0005/2026: the promoter view carries a 'Financial Indicators (Rs. in Lakhs)' block with a bare self-declared Net Worth NUMBER (populated on one of three: Rs 2,00,00,000) but no uploaded balance-sheet document anywhere in the documents list on any of the three projects checked. UP-RERA is No: the document grid was read on three real projects (51 rows, 20 distinct labels) and none resembles a balance sheet -- the closest is the Form REG-3 CA certificate, which certifies compliance rather than filing the statement itself. HARERA's Yes is real but softer than GujRERA's or JHARERA's actual uploaded statements: it rests on a Part-D compliance declaration ('Annex copy of the balance sheet of last 3 years: Yes') and a CA-certificate document referencing 'BOOKS OF ACCOUNTS/ BALANCE SHEET' -- no document in the 60-row library checked is itself labelled 'balance sheet'.</t>
+          <t>GujRERA findoc block. MahaRERA publishes nothing equivalent. Highest-value differential finding. JHARERA also files an audited balance sheet as a downloadable document, labelled directly on the project page. WBRERA is now Yes, confirmed live 2026-08-31 across 12 real projects checked: the application's own item 2 ('Audited balance sheet of the promoter for the preceding financial year and income tax returns... for three preceding financial years') carries real, downloaded files on every one -- e.g. 'Audited_Balance Sheet.pdf', 'Audited Balance Sheet 2024.PDF' -- already fetched by adapter_westbengal.py's existing document download, just never previously flagged as filed. Labelling is inconsistent enough (misspellings like 'blance sheet', combined balance-sheet+ITR files) that a downstream reader should still open the document rather than trust the label alone. TNRERA is Not published, audited live 2026-08-26 against TNRERA/29/BLG/0001/2026, /0004/2026 and /0005/2026: the promoter view carries a 'Financial Indicators (Rs. in Lakhs)' block with a bare self-declared Net Worth NUMBER (populated on one of three: Rs 2,00,00,000) but no uploaded balance-sheet document anywhere in the documents list on any of the three projects checked. UP-RERA is Not published: the document grid was read on three real projects (51 rows, 20 distinct labels) and none resembles a balance sheet -- the closest is the Form REG-3 CA certificate, which certifies compliance rather than filing the statement itself. HARERA's Yes is real but softer than GujRERA's or JHARERA's actual uploaded statements: it rests on a Part-D compliance declaration ('Annex copy of the balance sheet of last 3 years: Yes') and a CA-certificate document referencing 'BOOKS OF ACCOUNTS/ BALANCE SHEET' -- no document in the 60-row library checked is itself labelled 'balance sheet'.</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1701,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -1691,32 +1716,32 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
@@ -1731,7 +1756,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>GujRERA findoc block. TNRERA is No, same 'Financial Indicators' block and same three projects: 'Net Profit / Loss' is a bare self-declared number (Rs 72,16,670 on the one populated record), never a filed P&amp;L statement. UP-RERA is No, same three-project document-grid read as above. HARERA is No: 'profit and loss'/'profit &amp; loss' occurs zero times across four project detail pages checked (1444, 681, 3723, 431), against a single 'balance sheet' mention each -- the two are not filed together.</t>
+          <t>GujRERA findoc block. WBRERA's own disclosure item asks for a balance sheet and income-tax returns ONLY, never a P&amp;L statement by name -- checked live across the same 12 projects, no filename or label suggests one is filed separately, so this stays Not published rather than assuming a P&amp;L rides along inside one of the combined financial-statement PDFs. TNRERA is Not published, same 'Financial Indicators' block and same three projects: 'Net Profit / Loss' is a bare self-declared number (Rs 72,16,670 on the one populated record), never a filed P&amp;L statement. UP-RERA is Not published, same three-project document-grid read as above. HARERA is Not published: 'profit and loss'/'profit &amp; loss' occurs zero times across four project detail pages checked (1444, 681, 3723, 431), against a single 'balance sheet' mention each -- the two are not filed together.</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1768,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1758,7 +1783,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -1766,24 +1791,24 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
@@ -1798,7 +1823,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>GujRERA findoc block. JHARERA files three years of income-tax returns per project, also as downloadable documents. TNRERA is No, same block: 'Taxes Paid - IT (GST/ST)' is a single number that conflates income tax with GST/service tax (Rs 27,92,915 on the populated record) and no ITR document is filed anywhere in the three document sets checked. UP-RERA is No, same document-grid read. HARERA is No: 'income tax'/'ITR' occurs zero times across the same four pages.</t>
+          <t>GujRERA findoc block. JHARERA files three years of income-tax returns per project, also as downloadable documents. TNRERA is Not published, same block: 'Taxes Paid - IT (GST/ST)' is a single number that conflates income tax with GST/service tax (Rs 27,92,915 on the populated record) and no ITR document is filed anywhere in the three document sets checked. UP-RERA is Not published, same document-grid read. HARERA is Not published: 'income tax'/'ITR' occurs zero times across the same four pages.</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1835,17 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -1877,17 +1902,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -1897,12 +1922,12 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -1917,7 +1942,7 @@
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -1932,7 +1957,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>K-RERA /unregProjectList -- observed, not yet built. TNRERA stays Partial, but 'static (non-searchable)' is fixed as of 2026-08-26: both PDFs are NATIVE TEXT (confirmed live, zero OCR needed, unlike Delhi-RERA's REAT scans) and adapter_tamilnadu.py's parse_enforcement_pdf()/search_enforcement_lists_by_name() reads them with pdfplumber's table extraction -- 35 rows off the 5-page SCN list, 1,502 off the 118-page caution list, confirmed live end-to-end (searching 'Sivakaminathan' returns the real row). What did NOT change, because it is a finding about the authority's publication rather than a scraping gap: neither list covers a REGISTERED project under suo-moto scrutiny, only the unregistered-building enforcement pipeline -- 'Show Cause Notice issued for levy of penalty for non registration' and a 'Public Caution Notice' of buildings claimed as personal-use and therefore left unregistered. UP-RERA stays Partial for the opposite reason: the three adjacent registers (Abeyance, NCLT, Withdrawn Registration) named in the earlier audit are REAL pages, but their data loads via a WebService1.asmx POST that returned HTTP 500 on every parameter tried, including a real browser driving the page's own default (empty-parameter) call -- confirmed live 2026-08-26 this is the AUTHORITY'S OWN backend failing, not a request-shaping problem on this end, so nothing was built against a data source that cannot currently be read at all. HARERA is No: the only relevant menu item, 'Suo Motu (Projects) Cause List', is a hearing-schedule generator requiring a specific date and a CAPTCHA, not a browsable register; the only visible trace of suo-moto outcomes is inside HREAT's judgement text (case numbers containing 'MT' for Motu). Delhi-RERA is Yes: courtview/SuoMotoCases is a live, promoter-named, 1,797-row register of the authority's own-motion notices and orders -- the clearest 'projects under investigation' register found on any of the four new states; got an unwired parser in states/adapter_delhi.py.</t>
+          <t>K-RERA /unregProjectList -- observed, not yet built. TNRERA stays Partial, but 'static (non-searchable)' is fixed as of 2026-08-26: both PDFs are NATIVE TEXT (confirmed live, zero OCR needed, unlike Delhi-RERA's REAT scans) and adapter_tamilnadu.py's parse_enforcement_pdf()/search_enforcement_lists_by_name() reads them with pdfplumber's table extraction -- 35 rows off the 5-page SCN list, 1,502 off the 118-page caution list, confirmed live end-to-end (searching 'Sivakaminathan' returns the real row). What did NOT change, because it is a finding about the authority's publication rather than a scraping gap: neither list covers a REGISTERED project under suo-moto scrutiny, only the unregistered-building enforcement pipeline -- 'Show Cause Notice issued for levy of penalty for non registration' and a 'Public Caution Notice' of buildings claimed as personal-use and therefore left unregistered. UP-RERA stays Partial for the opposite reason: the three adjacent registers (Abeyance, NCLT, Withdrawn Registration) named in the earlier audit are REAL pages, but their data loads via a WebService1.asmx POST that returned HTTP 500 on every parameter tried, including a real browser driving the page's own default (empty-parameter) call -- confirmed live 2026-08-26 this is the AUTHORITY'S OWN backend failing, not a request-shaping problem on this end, so nothing was built against a data source that cannot currently be read at all. HARERA is Not published: the only relevant menu item, 'Suo Motu (Projects) Cause List', is a hearing-schedule generator requiring a specific date and a CAPTCHA, not a browsable register; the only visible trace of suo-moto outcomes is inside HREAT's judgement text (case numbers containing 'MT' for Motu). Delhi-RERA is Yes: courtview/SuoMotoCases is a live, promoter-named, 1,797-row register of the authority's own-motion notices and orders -- the clearest 'projects under investigation' register found on any of the four new states; got an unwired parser in states/adapter_delhi.py.</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1969,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1964,12 +1989,12 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -2011,17 +2036,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2031,22 +2056,22 @@
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
@@ -2066,7 +2091,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>K-RERA detail page carries a delay-reason table. TNRERA is No, audited live against TN/29/Building/0328/2024 whose register row reads 'Extension given upto 31.07.2026 Completed': its detail view (public-view2) has no delay-reason, extension-reason or revised-completion-date field across any of its 20 sections -- the extension text lives only as free text in the register's own Current Status column, never as a structured field, and never states WHY. UP-RERA is No: 'delay'/'reason'/'extension'/'revised' were grepped across three project pages with zero hits for 'delay' or 'reason'; the only adjacent field is a bare revised valid-upto date with no promoter-declared justification. HARERA is Partial: the project detail page carries structured 'Initial date of completion' and 'Likely date of completion' fields -- a computable delay signal -- but 'reason'/'justification' occurs zero times anywhere on the page, so there is no promoter-declared free-text reason, only the two dates.</t>
+          <t>K-RERA detail page carries a delay-reason table. TNRERA is Not published, audited live against TN/29/Building/0328/2024 whose register row reads 'Extension given upto 31.07.2026 Completed': its detail view (public-view2) has no delay-reason, extension-reason or revised-completion-date field across any of its 20 sections -- the extension text lives only as free text in the register's own Current Status column, never as a structured field, and never states WHY. UP-RERA is Not published: 'delay'/'reason'/'extension'/'revised' were grepped across three project pages with zero hits for 'delay' or 'reason'; the only adjacent field is a bare revised valid-upto date with no promoter-declared justification. HARERA is Partial: the project detail page carries structured 'Initial date of completion' and 'Likely date of completion' fields -- a computable delay signal -- but 'reason'/'justification' occurs zero times anywhere on the page, so there is no promoter-declared free-text reason, only the two dates.</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2103,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -2098,27 +2123,27 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not published</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
@@ -2133,7 +2158,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>K-RERA tracks NOC validity dates and whether renewed. TNRERA is revised from Partial to No, audited live 2026-08-26: the detail view does carry a 'Clearance / NOC Details' section, but its only fields are 'Clearance Type' (e.g. 'PWD &amp; RS') and 'Uploaded Document' -- confirmed on both a fresh 2026 registration and an already-extended 2024 one -- with no expiry date or renewal-status field anywhere in either. UP-RERA is No: zero genuine 'NOC' occurrences across three project pages and up-rera.in's full 153-link menu (the only raw-HTML hits were inside the base64 __VIEWSTATE blob). HARERA is No: the 'Statutory Approvals Status' table lists licence/clearance/NOC numbers each marked 'ALREADY BEEN OBTAINED' with a date -- but that date is when it was obtained, not an expiry or validity-end date, and no separate NOC-validity register exists.</t>
+          <t>K-RERA tracks NOC validity dates and whether renewed. TNRERA is revised from Partial to Not published, audited live 2026-08-26: the detail view does carry a 'Clearance / NOC Details' section, but its only fields are 'Clearance Type' (e.g. 'PWD &amp; RS') and 'Uploaded Document' -- confirmed on both a fresh 2026 registration and an already-extended 2024 one -- with no expiry date or renewal-status field anywhere in either. UP-RERA is Not published: zero genuine 'NOC' occurrences across three project pages and up-rera.in's full 153-link menu (the only raw-HTML hits were inside the base64 __VIEWSTATE blob). HARERA is Not published: the 'Statutory Approvals Status' table lists licence/clearance/NOC numbers each marked 'ALREADY BEEN OBTAINED' with a date -- but that date is when it was obtained, not an expiry or validity-end date, and no separate NOC-validity register exists.</t>
         </is>
       </c>
     </row>
@@ -2163,14 +2188,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Not published</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -2183,9 +2208,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>Unaudited</t>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="K25" s="10" t="inlineStr">
@@ -2200,7 +2225,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>Not confirmed either way for JHARERA or WBRERA -- neither adapter currently extracts a QPR-equivalent field, and nobody has checked whether either portal even publishes one.</t>
+          <t>JHARERA is now Yes, audited live 2026-08-31 against a real project (jharera.jharkhand.gov.in id 2625, PRANAMI BUILDERS): the flat/floor grid the adapter already reads for sold/unsold counts (adapter_jharkhand.py's own 'units' table, matched on 'flat no'+'sold status') carries its OWN per-unit 'Completion Status' column alongside Sold Status -- 101 rows, one per flat, each independently marked (every one 'Under Process' on this project, since it is still under construction). Real, structured, granular data that was already being fetched into `units` but never surfaced as a construction-progress finding. WBRERA is now Not published, audited live 2026-08-31: the project detail page (Crown, WBRERA/P/NOR/2025/002592) carries only SITE-WIDE marquee notices and a QPR_User_Manual.pdf link telling promoters a Quarterly Project Status Update is mandatory -- the mechanism exists as a filing requirement, but no per-project percentage, status or progress field is ever rendered on the page itself or in its document library. THE JHARERA PORTAL ITSELF IS UNSTABLE, not merely slow -- worth flagging beyond this one row. During the original audit 3 of 4 fetch attempts against the same URL (id 2625) timed out before one succeeded and produced the finding above. A follow-up retry session immediately after went 0 for 9 across three separate batches (40-50s timeouts, including three straight attempts at the exact same id that had worked minutes earlier) -- the portal was not reachable at all during that window. So JHARERA's Yes here rests on ONE successful live fetch, not a repeatable check; a future run finding this authority's portal unresponsive is the portal's own instability, not evidence the field is absent, and should not be read as a regression. HARERA is Partial, audited live 2026-08-31 across 8 real Gurugram-bench projects: the REP-I form's own construction-status fields are real but inconsistent in shape by project type. Plotted colonies carry a numeric 'Percentage completion Upto the date of application' for infrastructure development (85% and 59.24% and 12.30% seen on three different projects) plus a per-block-type qualitative status ('CIVIL STRUCTURE COMPLETED', 'WE HAVE RECEIVED OC ON 128 PLOTS'); group-housing/apartment projects instead carry only the qualitative narrative, no percentage. Both also carry an itemised estimated-vs-actual-expenditure table per infrastructure category (roads, water supply, drainage, electricity, etc.), which is a genuine progress signal in its own right. Stays Partial rather than Yes for two reasons: the field a reader gets depends on project type rather than being uniform, and there is no visible mechanism confirming these figures refresh on a recurring cadence rather than being frozen at the date of the last REP-I filing or amendment.</t>
         </is>
       </c>
     </row>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$22</definedName>
   </definedNames>
@@ -54,7 +54,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -79,11 +79,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -142,9 +137,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -709,6 +701,13 @@
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>14. Five of the sheet's 'Unaudited' cells were closed out live 2026-08-31. Professionals of record and Past-experience declarations are both genuinely Not published on HARERA -- its REP-I form has no section asking for either, confirmed by listing every numbered heading on the form across 7 real projects, not just the absence of a keyword. Past-experience is ALSO Not published on UP-RERA and TNRERA, checked on 4 and 3 real projects respectively -- a different finding from 'Promoter's other projects (track record)' above, which is about finding a promoter's OTHER filings by name match rather than a self-declared history on this one. Construction progress/QPR moved three ways at once: JHARERA to Yes (a genuine per-unit 'Completion Status' column already flowing through the adapter's own 'units' table but never surfaced), WBRERA to Not published (the page only carries a site-wide notice that QPR filing is mandatory, never a per-project figure), and HARERA to Partial (a real but project-type-dependent percentage-completion/status field). The JHARERA portal itself went down mid-audit -- 3 of 4 fetch attempts against the same URL timed out -- a reminder that an unreachable portal during a check is not the same finding as a confirmed absence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>15. Sheet B's last 'unaudited'/'Not built' row -- land records for the four non-Maharashtra states this pipeline touches -- is now four confirmed-live rows. Karnataka (Bhoomi) and Gujarat (AnyROR) are both free, District/Taluk(a)/village drill-downs behind a CAPTCHA text field, confirmed by inspecting the live DOM directly -- worth flagging because a first-pass automated read of both pages, working from page text alone, wrongly reported no CAPTCHA on either; the CAPTCHA element only exists once client-side JS renders it. AnyROR's own record-type dropdown carries 15 options, including a 'KNOW KHATA BY OWNER NAME' owner-name search. Uttar Pradesh splits across two separate systems: upbhulekh.gov.in's khatauni copy view is CAPTCHA-gated (plus a separate full-login flow for a fuller record, not audited here), while ekhasra.up.gov.in is a DIFFERENT system entirely for crop/khasra survey data, not ownership. Telangana is the one genuine surprise: dharani.telangana.gov.in, the system this codebase's own comments named, refuses every connection because Telangana retired Dharani for Bhu Bharati (bhubharati.telangana.gov.in) under a 2025 Act -- and Bhu Bharati's own public site routes every service through a mobile-OTP citizen login, no anonymous lookup path found anywhere, unlike the other three states' CAPTCHA-only public search. The two stale 'Dharani' comments this finding traces to (states/telangana.py, charter_document.py) were corrected in the same pass.</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2266,7 +2265,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>The free portal already returns every field. The extraction is what is broken -- no paid source is needed.</t>
+          <t>Maharashtra: the free portal already returns every field, and the extraction is what is broken -- no paid source is needed. Karnataka, Gujarat and Uttar Pradesh's own land-record portals are also free, CAPTCHA-gated, none built yet. Telangana is the exception: its own portal requires a mobile-OTP citizen account, not just a CAPTCHA.</t>
         </is>
       </c>
     </row>
@@ -2561,37 +2560,133 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Land records for other states</t>
+          <t>Karnataka land records (Bhoomi)</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Dharani (TG) / Bhoomi (KA) / AnyROR (GJ) / Bhulekh (UP)</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Not built</t>
+          <t>landrecords.karnataka.gov.in, RTC and Mutation Copy view</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>unaudited</t>
+          <t>Free + CAPTCHA</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Each is a separate system with its own identifier scheme, language and CAPTCHA.</t>
+          <t>Audited live 2026-09-01. District -&gt; Taluk -&gt; Hobli -&gt; Village drill-down, then survey number, then 'Fetch Survey Details' -- no login. A CAPTCHA text field (id=captchatextbox) IS present, confirmed by inspecting the live DOM directly rather than trusting a text summary of the page: an earlier automated read of this same portal claimed 'no explicit CAPTCHA mentioned', which was wrong -- the CAPTCHA is rendered by client-side JS and invisible to a fetch that doesn't run it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Gujarat land records (AnyROR)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>anyror.gujarat.gov.in, Rural Land Record</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Free + CAPTCHA</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Audited live 2026-09-01. One page, one District -&gt; Taluka -&gt; Village form, but a 15-option record-type dropdown behind it: VF-7 (survey details), VF-8A (khata/account), VF-6 (hakka patrak -- rights/mutation entries), 135-D mutation notice, revenue case details, and 'KNOW KHATA BY OWNER NAME' -- an owner-NAME search, confirmed present as a dropdown option though not opened this pass. A CAPTCHA text field (id=ContentPlaceHolder1_txt_captcha_1) is present, same DOM-inspection correction as Karnataka above -- a page-text summary alone also missed this one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh land records (Bhulekh + eKhasra)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>upbhulekh.gov.in (khatauni/ROR) and ekhasra.up.gov.in (khasra/crop survey) -- two separate systems, not one</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Free + CAPTCHA (khatauni) / Free (eKhasra geography step)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Audited live 2026-09-01. upbhulekh.gov.in's khatauni (Record of Rights) copy view is behind a CAPTCHA text field (name=captcha) on the homepage's own District/Tehsil/Pargana form; the site ALSO has a separate full account login ('खतौनी लॉगिन' / 'रियल टाइम खतौनी लॉगिन') for a fuller record, not audited here. ekhasra.up.gov.in is a DIFFERENT system for crop/khasra survey data (fasli-year crop entries, tree counts), not land ownership -- its District -&gt; Tehsil -&gt; Village selection step showed no CAPTCHA element in the DOM, but the final record-display step past village selection was not reached this pass, so that step is unconfirmed rather than assumed clean. Partial because the two systems only jointly cover part of what a 7/12-equivalent needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Telangana land records (Bhu Bharati, successor to Dharani)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>bhubharati.telangana.gov.in -- dharani.telangana.gov.in (the name this codebase has referenced) is retired</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Requires a mobile-OTP citizen account, not free-and-anonymous</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Audited live 2026-09-01. dharani.telangana.gov.in itself refused every connection tried (browser navigation AND a direct fetch both failed) -- not a network fluke on this end: Telangana's Revenue Department retired Dharani and replaced it with Bhu Bharati under the Telangana Bhu Bharati (Record of Rights in Land) Act, 2025, confirmed via web search, so this codebase's own comments citing 'Dharani (TG)' are now stale. bhubharati.telangana.gov.in DOES load, but every visible 'Transactional Services' and 'Information Services' tile on its homepage routes to /Citizen, a login gate asking for Mobile No. + Password/OTP with self-registration ('New user please Sign Up') -- no anonymous district/survey-number lookup path was found anywhere on the public site, unlike Karnataka, Gujarat or Uttar Pradesh above. A promoter's Telangana land details are therefore not reachable by this pipeline without an Indian mobile number to receive an OTP, which is a materially different access model from the other three states' CAPTCHA-only public search.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F13"/>
+  <autoFilter ref="A4:F16"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -2546,14 +2546,14 @@
           <t>Free -- page already fetched</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>observed</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>NOT currently parsed. The only independent check on the promoter's declared mortgage. National, so it belongs in the CIN workflow.</t>
+          <t>STALE ROW, RECONCILED 2026-09-01: this said 'observed'/'NOT currently parsed' months after it actually was -- company_profile_check.charges was wired up and confirmed live on 2026-08-19 (commit d0536e6), and Sheet C's own 'MCA CHARGE FILINGS' row has said confirmed-live since then. This row just never got updated to match. See that row for the live evidence (4 open charges, ~Rs 90.3 crore, HDFC Bank and Catalyst Trusteeship) -- kept here too, duplicated rather than deleted, because this is the only independent check on a promoter's declared mortgage and a reader scanning the land-records sheet for that fact should not be told it is still unbuilt.</t>
         </is>
       </c>
     </row>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -708,6 +708,20 @@
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>15. Sheet B's last 'unaudited'/'Not built' row -- land records for the four non-Maharashtra states this pipeline touches -- is now four confirmed-live rows. Karnataka (Bhoomi) and Gujarat (AnyROR) are both free, District/Taluk(a)/village drill-downs behind a CAPTCHA text field, confirmed by inspecting the live DOM directly -- worth flagging because a first-pass automated read of both pages, working from page text alone, wrongly reported no CAPTCHA on either; the CAPTCHA element only exists once client-side JS renders it. AnyROR's own record-type dropdown carries 15 options, including a 'KNOW KHATA BY OWNER NAME' owner-name search. Uttar Pradesh splits across two separate systems: upbhulekh.gov.in's khatauni copy view is CAPTCHA-gated (plus a separate full-login flow for a fuller record, not audited here), while ekhasra.up.gov.in is a DIFFERENT system entirely for crop/khasra survey data, not ownership. Telangana is the one genuine surprise: dharani.telangana.gov.in, the system this codebase's own comments named, refuses every connection because Telangana retired Dharani for Bhu Bharati (bhubharati.telangana.gov.in) under a 2025 Act -- and Bhu Bharati's own public site routes every service through a mobile-OTP citizen login, no anonymous lookup path found anywhere, unlike the other three states' CAPTCHA-only public search. The two stale 'Dharani' comments this finding traces to (states/telangana.py, charter_document.py) were corrected in the same pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>16. Sheet B's 'Lender, amount, satisfaction status' row said observed/'NOT currently parsed' months after it actually was -- Sheet C's own MCA-charge-filings row for the same underlying fact was confirmed live back in commit d0536e6, this one just never got updated to match. Reconciled 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>17. Credit-rating rationale documents -- WIRED IN 2026-09-01, not just found. CARE, India Ratings and Infomerics each embed a path to their own rationale document in a response this pipeline already fetches for the bare rating; none of the three were being extracted. Confirmed real by downloading/opening an actual document for each: Infomerics' carried a full 'Financials (Standalone)' table (Total Debt, Tangible Net Worth, EBITDA, PAT); CARE's carried real Total Income/Net Worth/Gearing figures; India Ratings renders its rationale as rich HTML rather than a PDF and went further still -- bookings, collections, cash flow from operations, forecast leverage ratios, a Strengths/Weaknesses key-rating-drivers section. Now wired into lookup_credit_rating's own return shape (rationale_url per agency), cited in the Charter's rating-comparison table, and registered as its own sources[] entry -- not left as an unused finding the way the WBRERA ITR gap was before it, too. ICRA stays a real, identified gap (a per-entity /Rationale/ShowRationaleReport?Id= mechanism exists, but resolving which Id belongs to which company needs more work); CRISIL is unchanged, since its own short inline excerpt predates this pass. This closes Sheet D's 'Credit-rating rationale documents' row -- removed from there since it is no longer unused.</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3115,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>ICRA / Infomerics press releases</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Partial</t>
+          <t>CARE / India Ratings / Infomerics</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -3114,19 +3128,19 @@
           <t>Free</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>observed</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>(unmapped -- Phase 4d)</t>
+          <t>credit_rating_check.promoter.ratings[].rationale_url</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Only the CURRENT rating is fetched today; the rationale endpoint is noted in code as not-yet-identified.</t>
+          <t>WIRED IN 2026-09-01, not just found: CARE, India Ratings and Infomerics all embed a path to their own rationale document in a response this pipeline already fetches for the bare rating -- Infomerics nests a PDF url four levels into a current instrument's own JSON; CARE's search response carries a CommonContent list of PDF filenames (date-sorted and Title-filtered here, since it mixes in group affiliates' filings under one shared CompanyID, unsorted); India Ratings renders its rationale as rich HTML, not a PDF, on its own page. All three confirmed by actually downloading/opening a real document -- Infomerics' carried a full 'Financials (Standalone)' table (Total Debt, Tangible Net Worth, EBITDA, PAT across two fiscal years); CARE's carried real Total Income/Net Worth/Gearing figures; India Ratings' page went further still -- bookings, collections, cash-flow-from-operations, forecast leverage ratios, a Strengths/Weaknesses key-rating-drivers section. company_charter.py's rating-comparison table now cites the rationale URL alongside the rating itself, and it is registered as its own sources[] entry. ICRA is the one gap left: a real per-entity rationale mechanism exists (/Rationale/ShowRationaleReport?Id=) but resolving which numeric Id belongs to a given company needs more reverse-engineering than this pass did. CRISIL is unchanged -- its own factsheet page already carried a short inline excerpt (the `rationale` key), not a document link, before this pass.</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3308,34 +3322,34 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Credit-rating rationale documents</t>
+          <t>K-RERA cost incurred vs estimated</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>ICRA / Infomerics</t>
+          <t>K-RERA detail page</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Rated promoters only</t>
+          <t>Karnataka projects</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Free route to revenue/debt/net-worth figures the MCA charges for.</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Financial-strength scores None everywhere today. This is a direct, free input.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>K-RERA cost incurred vs estimated</t>
+          <t>K-RERA delay reasons + NOC expiry</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -3350,61 +3364,61 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Financial-strength scores None everywhere today. This is a direct, free input.</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>K-RERA delay reasons + NOC expiry</t>
+          <t>Maha Bhulekh card fields</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>K-RERA detail page</t>
+          <t>Free portal, extraction broken</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Karnataka projects</t>
+          <t>Maharashtra projects</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Promoter-declared delay reasons and lapsed-NOC tracking; no equivalent elsewhere.</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Owner, area, tenure, encumbrance and mutation are all ON the card and none reach the document.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Maha Bhulekh card fields</t>
+          <t>JHARERA audited balance sheet + 3 years ITR</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Free portal, extraction broken</t>
+          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Maharashtra projects</t>
+          <t>Jharkhand projects</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Owner, area, tenure, encumbrance and mutation are all ON the card and none reach the document.</t>
+          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3416,12 +3430,12 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>JHARERA audited balance sheet + 3 years ITR</t>
+          <t>JHARERA rejected + surrendered registration lists</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
+          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3431,34 +3445,34 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>JHARERA rejected + surrendered registration lists</t>
+          <t>WBRERA defaulters list</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
+          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Jharkhand projects</t>
+          <t>West Bengal projects</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
+          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -3470,76 +3484,76 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>WBRERA defaulters list</t>
+          <t>UP-RERA de-registered/defaulter list</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
+          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>West Bengal projects</t>
+          <t>Uttar Pradesh projects</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>UP-RERA de-registered/defaulter list</t>
+          <t>HARERA cancelled/defaulter projects</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
+          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Uttar Pradesh projects</t>
+          <t>Haryana projects</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>HARERA cancelled/defaulter projects</t>
+          <t>TNRERA penalty register</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
+          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Haryana projects</t>
+          <t>Tamil Nadu projects</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
+          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -3551,22 +3565,22 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>TNRERA penalty register</t>
+          <t>TNRERA unregistered-project enforcement PDFs</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
+          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Tamil Nadu projects</t>
+          <t>Tamil Nadu projects/promoters</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
+          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -3578,39 +3592,39 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>TNRERA unregistered-project enforcement PDFs</t>
+          <t>Delhi-RERA suo-moto register</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
+          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Tamil Nadu projects/promoters</t>
+          <t>Delhi projects</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Delhi-RERA suo-moto register</t>
+          <t>Delhi-RERA execution register</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
+          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -3620,24 +3634,24 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Delhi-RERA execution register</t>
+          <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
+          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3647,44 +3661,17 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Delhi projects</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
           <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised.</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E22"/>
+  <autoFilter ref="A4:E21"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A - RERA by authority'!$A$4:$M$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B - CTS land records'!$A$4:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C - CIN corporate'!$A$4:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D - Available but unused'!$A$4:$E$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -722,6 +722,13 @@
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>17. Credit-rating rationale documents -- WIRED IN 2026-09-01, not just found. CARE, India Ratings and Infomerics each embed a path to their own rationale document in a response this pipeline already fetches for the bare rating; none of the three were being extracted. Confirmed real by downloading/opening an actual document for each: Infomerics' carried a full 'Financials (Standalone)' table (Total Debt, Tangible Net Worth, EBITDA, PAT); CARE's carried real Total Income/Net Worth/Gearing figures; India Ratings renders its rationale as rich HTML rather than a PDF and went further still -- bookings, collections, cash flow from operations, forecast leverage ratios, a Strengths/Weaknesses key-rating-drivers section. Now wired into lookup_credit_rating's own return shape (rationale_url per agency), cited in the Charter's rating-comparison table, and registered as its own sources[] entry -- not left as an unused finding the way the WBRERA ITR gap was before it, too. ICRA stays a real, identified gap (a per-entity /Rationale/ShowRationaleReport?Id= mechanism exists, but resolving which Id belongs to which company needs more work); CRISIL is unchanged, since its own short inline excerpt predates this pass. This closes Sheet D's 'Credit-rating rationale documents' row -- removed from there since it is no longer unused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>18. IGR Maharashtra e-Search -- Sheet B's last two 'observed' rows, closed live 2026-09-01 with a REAL pulled result, not just a reachable form. freesearchigrservice.maharashtra.gov.in offers two free, CAPTCHA-gated search modes (Property Details: Year/District/Village-or-Area/Survey-CTS-Milkat-Gat-Plot No.; Document Number: Registration Type/District, all 37, genuinely statewide/SRO/Year/Doc No.). Document Number/SRO Mumbai 9 (Andheri)/2024/#100 returned a real registered Leave &amp; License agreement -- seller and purchaser named, full property description, AND the actual consideration (Rs 44,100/month plus Rs 5,29,200 advance) -- all in the result row itself, no extra click. Genuine limitation found along the way, from the site's own FAQ: Power of Attorney and Will deeds are excluded from search entirely. Equitable mortgages share the identical mechanism and evidence -- a Notice of Intimation is just one more possible deed-name value, not a separately filterable category -- but no live mortgage example was actually pulled this pass, so that row confirms the channel, not a specific instance. Also found: the page's own 'CERSAI Search' button is an integrated postback on this same portal, not an external redirect. Added to Sheet D as a new high-value, unbuilt finding -- nothing in this pipeline calls this portal yet, and it is the only independent, party-named check on a promoter's registered dealings this pipeline has found for Maharashtra.</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2490,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>IGR Maharashtra e-Search (Index II)</t>
+          <t>IGR Maharashtra e-Search (freesearchigrservice.maharashtra.gov.in)</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2496,14 +2503,14 @@
           <t>Free + CAPTCHA</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>observed</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Mumbai from 1985; other districts digitised from 2002.</t>
+          <t>Audited live 2026-09-01 with a REAL result, not just a reachable form. Two search modes, both free and CAPTCHA-gated (confirmed via DOM inspection, not just a page-text guess): 'Property Details' (Year -&gt; District -&gt; Village/Area, an autocomplete text field paired with a dropdown -&gt; Survey/CTS/Milkat/Gat/Plot No.; a name-based search is also offered once a property number is entered) and 'Document Number' (Registration Type [eFiling/eRegistration/Regular/iSarita 2.0] -&gt; District, all 37 -- this mode is genuinely statewide, not Mumbai-only -&gt; SRO -&gt; Year -&gt; Doc No.). Document Number/SRO Mumbai 9 (Andheri)/2024/#100 returned a real registered Leave &amp; License agreement dated 03/01/2024 -- Seller/Lessor 'Ramesh Babulal Shah', Purchaser/Lessee 'M/s Matushri Impex' (through partner Ramesh T. Bhalani), full property description (Bandra Kurla Complex premises, CTS No. 4207) AND consideration (monthly rent Rs 44,100 plus Rs 5,29,200 advance for the first 12 months) -- all present in the RESULT LIST ROW ITSELF, no further click needed. Each row also carries an 'IndexII' button (a further postback, __doPostBack('RegistrationGrid','indexII$0')) documented in the site's own User Guide as opening a fuller Index II view in a separate window -- present and clickable, but its own content was NOT captured this pass (the popup did not materialize in this environment), so that specific view stays unconfirmed rather than assumed. A real, stated limitation from the site's own FAQ: Power of Attorney and Will deeds are NOT available in search results. Mumbai city and Suburban districts go back to 1985; 'selected offices' elsewhere now reach back before the earlier 2002 baseline too, per the site's own notice.</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2522,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>IGR Notice of Intimation</t>
+          <t>IGR Notice of Intimation (freesearchigrservice.maharashtra.gov.in)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -2528,14 +2535,14 @@
           <t>Free + CAPTCHA</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>observed</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>confirmed-live</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Compulsory in MAHARASHTRA AND GUJARAT ONLY. This is why CERSAI is not needed for those two states.</t>
+          <t>The MECHANISM is confirmed live, sharing the exact same interface, schema and evidence as the row above -- 'Registration Type' (eFiling/eRegistration/Regular/iSarita 2.0) is a filing-channel category, not a deed-type filter, so a Notice of Intimation is just one of many possible 'DName' (deed name) values a search can return, discoverable the same way any other deed is: by its own document number, or by opening a property's full document list. No live example of an actual Notice of Intimation was captured this pass -- the one real result pulled was a Leave &amp; License agreement -- so this confirms the CHANNEL, not a specific mortgage instance. Separately confirmed: the 'CERSAI Search' button on this same page is an INTEGRATED postback on igr's own portal (__doPostBack with a distinct 'aa' validation group), not an external redirect to cersai.org.in -- worth knowing before assuming a CERSAI cross-check means leaving this site. 'Compulsory in MAHARASHTRA AND GUJARAT ONLY, which is why CERSAI is not needed for those two states' is the pre-existing legal claim this row already carried; it was not independently re-verified this pass, since the portal itself doesn't state its own legal basis anywhere in the UI.</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3403,22 +3410,22 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>JHARERA audited balance sheet + 3 years ITR</t>
+          <t>IGR Maharashtra registered-deed search</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
+          <t>freesearchigrservice.maharashtra.gov.in, confirmed live 2026-09-01 (not built)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Jharkhand projects</t>
+          <t>Maharashtra projects</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
+          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. A real result already pulled carries seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. Also carries an integrated CERSAI cross-search on the same page. Nothing calls this portal yet.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3430,12 +3437,12 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>JHARERA rejected + surrendered registration lists</t>
+          <t>JHARERA audited balance sheet + 3 years ITR</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
+          <t>adapter_jharkhand.py document library (labelled, downloaded)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -3445,34 +3452,34 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Same gap as GujRERA's findoc block: the financial-strength sub-metric scores None for every project regardless of state. This would score it for JH too.</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>WBRERA defaulters list</t>
+          <t>JHARERA rejected + surrendered registration lists</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
+          <t>REJECTED_LIST / SURRENDERED_LIST, imported into the adapter but never fetched</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>West Bengal projects</t>
+          <t>Jharkhand projects</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
+          <t>A rejected or surrendered registration is diligence material with no equivalent on MahaRERA. The URLs are already wired into the import list; nothing calls them yet.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -3484,76 +3491,76 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>UP-RERA de-registered/defaulter list</t>
+          <t>WBRERA defaulters list</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
+          <t>adapter_westbengal.fetch_defaulters() -- written, unwired, untested live</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Uttar Pradesh projects</t>
+          <t>West Bengal projects</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>17 rejected/defaulting applications keyed by name -- a cheap, direct red-flag input. The parser exists but is called from nowhere in acquire() or the litigation sweep.</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>HARERA cancelled/defaulter projects</t>
+          <t>UP-RERA de-registered/defaulter list</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
+          <t>adapter_uttarpradesh.fetch_defaulters() -- written, unwired, live-verified 2026-08-26 (72 rows)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Haryana projects</t>
+          <t>Uttar Pradesh projects</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Named by promoter outright -- ANSAL PROPERTIES &amp; INFRASTRUCTURE LIMITED is on it. Reachable only via an ASP.NET postback, not a plain URL, which is why nothing had fetched it before.</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>TNRERA penalty register</t>
+          <t>HARERA cancelled/defaulter projects</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
+          <t>adapter_haryana.fetch_defaulter_projects() -- written, unwired, live-verified 2026-08-26 (23 Panchkula + 5 Gurugram)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Tamil Nadu projects</t>
+          <t>Haryana projects</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
+          <t>Distinct from the already-imported LAPSED_PROJECTS URL, which is validity expiry, not an authority action -- conflating the two would understate lapsed rows as defaults or vice versa.</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -3565,22 +3572,22 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>TNRERA unregistered-project enforcement PDFs</t>
+          <t>TNRERA penalty register</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
+          <t>adapter_tamilnadu.fetch_penalty_notices() -- written, unwired, live-verified 2026-08-26 (147 rows across Building + Layout)</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Tamil Nadu projects/promoters</t>
+          <t>Tamil Nadu projects</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
+          <t>Names promoter, project and the penalty amount levied -- TNRERA's own closest equivalent to a defaulters list, titled 'Penalty' rather than that.</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -3592,39 +3599,39 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Delhi-RERA suo-moto register</t>
+          <t>TNRERA unregistered-project enforcement PDFs</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
+          <t>adapter_tamilnadu.search_enforcement_lists_by_name() -- written, unwired, live-verified 2026-08-26 (35 + 1,502 rows, native-text PDFs, no OCR needed)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Delhi projects</t>
+          <t>Tamil Nadu projects/promoters</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>The show-cause and personal-use-caution lists, now actually searchable by name rather than merely linked as static PDFs. Ceiling is real, not fixable in code: both cover UNREGISTERED sites, never a registered project under suo-moto scrutiny.</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Delhi-RERA execution register</t>
+          <t>Delhi-RERA suo-moto register</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
+          <t>adapter_delhi.parse_suo_moto_register() -- written, unwired, live-verified 2026-08-26 (1,797 rows)</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -3634,44 +3641,71 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Names a Respondent/Promoter and project per row -- the clearest 'projects under investigation' signal found on any of the four newest states, and Delhi otherwise has no per-project record at all.</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Delhi-RERA execution register</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>adapter_delhi.parse_execution_register() -- written, unwired, live-verified 2026-08-26 (7,493 rows)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Delhi projects</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Orders referred for enforcement because the promoter (named as Judgement Debtor) did not comply -- the authority's own closest equivalent to a defaulters list.</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>Delhi-RERA Appellate Tribunal (REAT) register, WITH party names</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>adapter_delhi.build_appeal_party_index() / search_appeals_by_party() -- written, unwired, live-verified 2026-08-26 (437/505 rows named, 481 PDFs OCR'd)</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Delhi projects</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>The register itself names no party -- not linked from any Delhi-RERA page either, found only by web search -- but every row links a scanned judgement PDF whose own case caption does. OCRing just the PDFs' first pages (PyMuPDF native text, confirmed zero on every sample -- Tesseract fallback) turned an unsearchable register into one where search_appeals_by_party('Parsvnath') returns 27 real hits. The only gaps are the authority's own 63 broken PDF links and 5 older (2021-2022) PDFs in a caption shape not yet recognised.</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E21"/>
+  <autoFilter ref="A4:E22"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>freesearchigrservice.maharashtra.gov.in, confirmed live 2026-09-01 (not built)</t>
+          <t>igr_maharashtra_search.py -- BUILT 2026-09-01, human-in-the-loop like up_captcha_search.py/cts_resolve.py, not wired into run_company_charter()</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. A real result already pulled carries seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. Also carries an integrated CERSAI cross-search on the same page. Nothing calls this portal yet.</t>
+          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. search_by_document_number() is confirmed against a real pulled result: seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. search_by_property() is also built (form mechanics confirmed live), but its OWN result table shape is not yet confirmed against a real row, unlike document-number search. Also carries an integrated CERSAI cross-search on the same page, not yet driven by either function. A standalone script, run by a human, same as every other CAPTCHA-gated tool here -- not called from the automated Charter pipeline.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">

--- a/docs/RERA_Data_Coverage.xlsx
+++ b/docs/RERA_Data_Coverage.xlsx
@@ -3425,7 +3425,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. search_by_document_number() is confirmed against a real pulled result: seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. search_by_property() is also built (form mechanics confirmed live), but its OWN result table shape is not yet confirmed against a real row, unlike document-number search. Also carries an integrated CERSAI cross-search on the same page, not yet driven by either function. A standalone script, run by a human, same as every other CAPTCHA-gated tool here -- not called from the automated Charter pipeline.</t>
+          <t>An independent, free, party-named check on registrations against a property/CTS number or a specific document number -- CAPTCHA-gated but otherwise unauthenticated. search_by_document_number() is confirmed against a real pulled result: seller/purchaser names, full property description and the ACTUAL CONSIDERATION AMOUNT in one row, no further click needed -- a direct corroboration (or contradiction) of a promoter's declared land dealings that nothing else in this pipeline checks independently. search_by_property() is also built and, confirmed live chasing a real Pune search, turned out to need THREE separate regions (mumbai/rest_of_maharashtra/urban), each its own field ids and cascade shape -- the landing page's default tab covers only the two Mumbai districts, not the whole state as it first appeared. A locality can sit in either the rural or urban region depending on how it was annexed: Pune's Market Yard (Gulatekadi) is under 'urban', not the rural taluka/village list a human would try first, and guessing wrong doesn't error -- it just returns a real but unrelated village list. All three regions' form mechanics are confirmed live end-to-end up to the CAPTCHA gate; the RESULT TABLE'S OWN SHAPE for search_by_property is still not confirmed against a real row for any of them, unlike document-number search. Also carries an integrated CERSAI cross-search on the same page, not yet driven by either function. A standalone script, run by a human, same as every other CAPTCHA-gated tool here -- not called from the automated Charter pipeline.</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
